--- a/plan/Nodejs_Skillup_Plan_202608.xlsx
+++ b/plan/Nodejs_Skillup_Plan_202608.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nezha/Documents/nodejs-skillup/plan/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="REPO_ROOT/plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69715CA3-9642-274A-BEBC-9867D83F25C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -28,7 +28,7 @@
     <t>目标</t>
   </si>
   <si>
-    <t>对齐当前在招的两个方向（React + Node.js / React + Java）与现有能力画像（React / Next / TS、Node / Express），在主栈上补齐服务端交付链路（部署 / 排障 / CI）与 AI 协作能力。Java 基础按 PeM 建议穿插纳入，不单独占周。产出继续以 GitHub 仓库体现：https://github.com/NiceFreak/nodejs-skillup</t>
+    <t>覆盖 React + Node.js / React + Java 两条技术方向，并在 React / Next / TypeScript、Node / Express 基础上补齐服务端交付链路（部署 / 排障 / CI）与 AI 协作能力。Java 基础穿插纳入，不单独占周；产出由本仓库记录。</t>
   </si>
   <si>
     <t>周期</t>
@@ -82,7 +82,7 @@
     <t>可观测性与线上排障</t>
   </si>
   <si>
-    <t>把「出了问题怎么查」从经验变成方法；对应 support / maintenance 类岗位的核心考察点</t>
+    <t>把「出了问题怎么查」从经验变成方法，形成跨技术栈可迁移的系统化排障能力</t>
   </si>
   <si>
     <t>日志规范与集中收集（pino / winston + 日志轮转）；基础监控与告警；进程与内存问题定位（结合 Node 内存模型）；常见故障模式（端口占用、证书过期、磁盘满、OOM、反代配置错误）；runbook 与事故复盘写法</t>
@@ -169,10 +169,10 @@
     <t>Java 基础</t>
   </si>
   <si>
-    <t>按 PeM 建议纳入。范围：语法与 JVM 生态基础、Maven 依赖与打包、Spring Boot 最小服务；随第 1 周（部署一个 jar 服务）与第 3 周（Maven 构建 job）的主线带出，不单独占周。诚实边界：本轮目标是能读懂代码并搭起最小服务，不声称 Java 生产能力。</t>
-  </si>
-  <si>
-    <t>按 PeM 建议纳入。范围：语法与 JVM 生态基础、Maven 依赖与打包、Spring Boot 最小服务；随第 1 周（部署 jar）与第 3 周（Maven job）作为主线完成后的 stretch 带出，不单独占周、不阻断当周验收。诚实边界：本轮目标是能读懂代码并搭起最小服务，不声称 Java 生产能力。</t>
+    <t>按当前学习范围纳入。范围：语法与 JVM 生态基础、Maven 依赖与打包、Spring Boot 最小服务；随第 1 周（部署一个 jar 服务）与第 3 周（Maven 构建 job）的主线带出，不单独占周。诚实边界：本轮目标是能读懂代码并搭起最小服务，不声称 Java 生产能力。</t>
+  </si>
+  <si>
+    <t>按当前学习范围纳入。范围：语法与 JVM 生态基础、Maven 依赖与打包、Spring Boot 最小服务；随第 1 周（部署 jar）与第 3 周（Maven job）作为主线完成后的 stretch 带出，不单独占周、不阻断当周验收。诚实边界：本轮目标是能读懂代码并搭起最小服务，不声称 Java 生产能力。</t>
   </si>
   <si>
     <t>每周产出完成后，用 5–10 分钟整理成一段可口述的项目叙述（背景 → 问题 → 做法 → 结果 → 边界）。</t>
@@ -190,10 +190,10 @@
     <t>第 1–3 周为一条连续主线（手工部署 → 会看会修 → 自动化发布），第 4 周将其中的重复动作工具化，第 5 周为前端专项。</t>
   </si>
   <si>
-    <t>每周产出相互独立，任一周单独交付即成立；中途若进项目则自动 rolloff。</t>
-  </si>
-  <si>
-    <t>第 1–3 周复用同一环境形成连续主线（手工部署 → 会看会修 → 自动化发布）；每周交付证据和项目叙述可独立验收。中途若进项目则按当周已完成证据收口并 rolloff。</t>
+    <t>每周产出相互独立，任一周单独交付即成立；中途若范围变化则按已完成证据收口。</t>
+  </si>
+  <si>
+    <t>第 1–3 周复用同一环境形成连续主线（手工部署 → 会看会修 → 自动化发布）；每周交付证据和项目叙述可独立验收。中途若范围变化则按当周已完成证据收口。</t>
   </si>
   <si>
     <t>服务可从公网访问且证书有效；仓库中有一份部署文档，按文档可重新走一遍；能说明每一层（Nginx / Node / systemd / 证书 / 防火墙）各自解决什么问题；MongoDB 不暴露公网且只使用空库或脱敏数据。Java stretch 不阻断 W9；若执行，需先记录内存余量，并能说明 Node 与 JVM 在 runtime 和启动契约上的差异</t>
